--- a/MASTER/cluster_plots_loadings/agg/pca_results_agg.xlsx
+++ b/MASTER/cluster_plots_loadings/agg/pca_results_agg.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,11 +444,6 @@
           <t>PC2</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PC3</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -462,9 +457,6 @@
       <c r="C2" t="n">
         <v>0.1680546090256276</v>
       </c>
-      <c r="D2" t="n">
-        <v>0.6339371786505779</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -478,9 +470,6 @@
       <c r="C3" t="n">
         <v>0.06801481244504431</v>
       </c>
-      <c r="D3" t="n">
-        <v>0.003172525814654271</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -494,9 +483,6 @@
       <c r="C4" t="n">
         <v>0.007838290360246204</v>
       </c>
-      <c r="D4" t="n">
-        <v>-0.004493012044638082</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -510,9 +496,6 @@
       <c r="C5" t="n">
         <v>0.46456309451552</v>
       </c>
-      <c r="D5" t="n">
-        <v>-0.1431694081626731</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -526,9 +509,6 @@
       <c r="C6" t="n">
         <v>0.04155987558594835</v>
       </c>
-      <c r="D6" t="n">
-        <v>-0.0108822653174053</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -542,9 +522,6 @@
       <c r="C7" t="n">
         <v>0.6071411384687528</v>
       </c>
-      <c r="D7" t="n">
-        <v>-0.2825572337138719</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -558,9 +535,6 @@
       <c r="C8" t="n">
         <v>0.4676192345389734</v>
       </c>
-      <c r="D8" t="n">
-        <v>-0.1233490105223263</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -574,9 +548,6 @@
       <c r="C9" t="n">
         <v>0.04644898335646994</v>
       </c>
-      <c r="D9" t="n">
-        <v>-0.004324907516542495</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -590,9 +561,6 @@
       <c r="C10" t="n">
         <v>0.01346980566927267</v>
       </c>
-      <c r="D10" t="n">
-        <v>-0.007433755976051937</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -606,9 +574,6 @@
       <c r="C11" t="n">
         <v>0.01669204110145536</v>
       </c>
-      <c r="D11" t="n">
-        <v>0.006130208818825306</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -622,9 +587,6 @@
       <c r="C12" t="n">
         <v>-0.06789889884648816</v>
       </c>
-      <c r="D12" t="n">
-        <v>-0.118020183008</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -638,9 +600,6 @@
       <c r="C13" t="n">
         <v>0.2828436416323297</v>
       </c>
-      <c r="D13" t="n">
-        <v>0.5071088761496262</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -654,9 +613,6 @@
       <c r="C14" t="n">
         <v>-0.002585555619074323</v>
       </c>
-      <c r="D14" t="n">
-        <v>0.002048886521419602</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -670,9 +626,6 @@
       <c r="C15" t="n">
         <v>0.06783823401477408</v>
       </c>
-      <c r="D15" t="n">
-        <v>0.01375484815050853</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -686,9 +639,6 @@
       <c r="C16" t="n">
         <v>-0.114273812707662</v>
       </c>
-      <c r="D16" t="n">
-        <v>-0.4528370053778373</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -702,9 +652,6 @@
       <c r="C17" t="n">
         <v>0.002135748655610592</v>
       </c>
-      <c r="D17" t="n">
-        <v>0.0007843609516559873</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -718,9 +665,6 @@
       <c r="C18" t="n">
         <v>0.1826484946121057</v>
       </c>
-      <c r="D18" t="n">
-        <v>-0.06271552995771125</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -734,9 +678,6 @@
       <c r="C19" t="n">
         <v>0.03005764391480358</v>
       </c>
-      <c r="D19" t="n">
-        <v>0.03599957034229762</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -750,9 +691,6 @@
       <c r="C20" t="n">
         <v>0.008409924822976518</v>
       </c>
-      <c r="D20" t="n">
-        <v>0.00308857347056098</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -765,9 +703,6 @@
       </c>
       <c r="C21" t="n">
         <v>0.151661465463071</v>
-      </c>
-      <c r="D21" t="n">
-        <v>-0.02702036676557912</v>
       </c>
     </row>
   </sheetData>
@@ -781,7 +716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -795,11 +730,6 @@
           <t>PC2</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PC3</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -813,9 +743,6 @@
       <c r="C2" t="n">
         <v>-0.114273812707662</v>
       </c>
-      <c r="D2" t="n">
-        <v>-0.4528370053778373</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -829,9 +756,6 @@
       <c r="C3" t="n">
         <v>0.2828436416323297</v>
       </c>
-      <c r="D3" t="n">
-        <v>0.5071088761496262</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -845,56 +769,44 @@
       <c r="C4" t="n">
         <v>0.6071411384687528</v>
       </c>
-      <c r="D4" t="n">
-        <v>-0.2825572337138719</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Aluminium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1157348996745892</v>
+        <v>-0.08220537317096409</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1680546090256276</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.6339371786505779</v>
+        <v>0.4676192345389734</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Coal</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.08220537317096409</v>
+        <v>0.01485059817299969</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4676192345389734</v>
-      </c>
-      <c r="D6" t="n">
-        <v>-0.1233490105223263</v>
+        <v>0.46456309451552</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Coal</t>
+          <t>Aluminium</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01485059817299969</v>
+        <v>0.1157348996745892</v>
       </c>
       <c r="C7" t="n">
-        <v>0.46456309451552</v>
-      </c>
-      <c r="D7" t="n">
-        <v>-0.1431694081626731</v>
+        <v>0.1680546090256276</v>
       </c>
     </row>
     <row r="8">
@@ -909,40 +821,31 @@
       <c r="C8" t="n">
         <v>0.1826484946121057</v>
       </c>
-      <c r="D8" t="n">
-        <v>-0.06271552995771125</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01646364721566061</v>
+        <v>0.003358172337800761</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.06789889884648816</v>
-      </c>
-      <c r="D9" t="n">
-        <v>-0.118020183008</v>
+        <v>0.151661465463071</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.003358172337800761</v>
+        <v>0.01646364721566061</v>
       </c>
       <c r="C10" t="n">
-        <v>0.151661465463071</v>
-      </c>
-      <c r="D10" t="n">
-        <v>-0.02702036676557912</v>
+        <v>-0.06789889884648816</v>
       </c>
     </row>
     <row r="11">
@@ -957,72 +860,57 @@
       <c r="C11" t="n">
         <v>0.06783823401477408</v>
       </c>
-      <c r="D11" t="n">
-        <v>0.01375484815050853</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Tin</t>
+          <t>Bauxite</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.01244322254503104</v>
+        <v>0.0009731086661451758</v>
       </c>
       <c r="C12" t="n">
-        <v>0.03005764391480358</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.03599957034229762</v>
+        <v>0.06801481244504431</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Bauxite</t>
+          <t>Cobalt</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0009731086661451758</v>
+        <v>-0.01491486038023693</v>
       </c>
       <c r="C13" t="n">
-        <v>0.06801481244504431</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.003172525814654271</v>
+        <v>0.04155987558594835</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Cobalt</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.01491486038023693</v>
+        <v>0.002662812684716794</v>
       </c>
       <c r="C14" t="n">
-        <v>0.04155987558594835</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.0108822653174053</v>
+        <v>0.04644898335646994</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Tin</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.002662812684716794</v>
+        <v>-0.01244322254503104</v>
       </c>
       <c r="C15" t="n">
-        <v>0.04644898335646994</v>
-      </c>
-      <c r="D15" t="n">
-        <v>-0.004324907516542495</v>
+        <v>0.03005764391480358</v>
       </c>
     </row>
     <row r="16">
@@ -1037,9 +925,6 @@
       <c r="C16" t="n">
         <v>0.01669204110145536</v>
       </c>
-      <c r="D16" t="n">
-        <v>0.006130208818825306</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -1053,9 +938,6 @@
       <c r="C17" t="n">
         <v>0.01346980566927267</v>
       </c>
-      <c r="D17" t="n">
-        <v>-0.007433755976051937</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1069,9 +951,6 @@
       <c r="C18" t="n">
         <v>0.008409924822976518</v>
       </c>
-      <c r="D18" t="n">
-        <v>0.00308857347056098</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -1085,9 +964,6 @@
       <c r="C19" t="n">
         <v>0.007838290360246204</v>
       </c>
-      <c r="D19" t="n">
-        <v>-0.004493012044638082</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -1101,9 +977,6 @@
       <c r="C20" t="n">
         <v>-0.002585555619074323</v>
       </c>
-      <c r="D20" t="n">
-        <v>0.002048886521419602</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -1116,9 +989,6 @@
       </c>
       <c r="C21" t="n">
         <v>0.002135748655610592</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.0007843609516559873</v>
       </c>
     </row>
   </sheetData>
@@ -1132,7 +1002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1151,11 +1021,6 @@
           <t>PC2</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PC3</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -1164,13 +1029,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-3.271414391415495</v>
+        <v>6.225726585003693</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.8480059788258312</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.5907976080798988</v>
+        <v>0.4201768051518999</v>
       </c>
     </row>
     <row r="3">
@@ -1180,13 +1042,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.582744422924895</v>
+        <v>-3.227562172924972</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9927410848549549</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.6047210634087534</v>
+        <v>-0.9817659166880812</v>
       </c>
     </row>
     <row r="4">
@@ -1196,13 +1055,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-3.895659661367456</v>
+        <v>2.133144747243484</v>
       </c>
       <c r="C4" t="n">
-        <v>3.875318023065608</v>
-      </c>
-      <c r="D4" t="n">
-        <v>-1.542205563870714</v>
+        <v>-0.5647905338731611</v>
       </c>
     </row>
     <row r="5">
@@ -1212,13 +1068,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.354275972825491</v>
+        <v>-2.736498202368519</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.759705702369397</v>
-      </c>
-      <c r="D5" t="n">
-        <v>-1.556677763635299</v>
+        <v>3.836272494677326</v>
       </c>
     </row>
   </sheetData>
@@ -1232,7 +1085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1251,11 +1104,6 @@
           <t>PC2</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PC3</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -1264,13 +1112,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3590715966582932</v>
+        <v>1.303952241171763</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8561006915335372</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.5191436308261053</v>
+        <v>1.972977843009895</v>
       </c>
     </row>
     <row r="3">
@@ -1280,13 +1125,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.140237087199823</v>
+        <v>0.5468954606992731</v>
       </c>
       <c r="C3" t="n">
-        <v>2.077240060615073</v>
-      </c>
-      <c r="D3" t="n">
-        <v>2.449006416962581</v>
+        <v>0.5695173293097336</v>
       </c>
     </row>
     <row r="4">
@@ -1296,13 +1138,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2136504969746562</v>
+        <v>1.127807601783646</v>
       </c>
       <c r="C4" t="n">
-        <v>1.731841515415532</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.6510379631466937</v>
+        <v>1.857566990815179</v>
       </c>
     </row>
     <row r="5">
@@ -1312,13 +1151,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.12329111939165</v>
+        <v>2.310490597727751</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6272208842499121</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1.233071101321312</v>
+        <v>1.730648438290521</v>
       </c>
     </row>
   </sheetData>
@@ -1354,7 +1190,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -1364,7 +1200,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -1374,7 +1210,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -1384,7 +1220,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1398,7 +1234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1430,7 +1266,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-3.271414391415495</v>
+        <v>6.225726585003693</v>
       </c>
     </row>
     <row r="3">
@@ -1445,7 +1281,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4.582744422924895</v>
+        <v>-3.227562172924972</v>
       </c>
     </row>
     <row r="4">
@@ -1460,7 +1296,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-3.895659661367456</v>
+        <v>2.133144747243484</v>
       </c>
     </row>
     <row r="5">
@@ -1475,7 +1311,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.354275972825491</v>
+        <v>-2.736498202368519</v>
       </c>
     </row>
     <row r="6">
@@ -1490,7 +1326,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.8480059788258312</v>
+        <v>0.4201768051518999</v>
       </c>
     </row>
     <row r="7">
@@ -1505,7 +1341,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.9927410848549549</v>
+        <v>-0.9817659166880812</v>
       </c>
     </row>
     <row r="8">
@@ -1520,7 +1356,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3.875318023065608</v>
+        <v>-0.5647905338731611</v>
       </c>
     </row>
     <row r="9">
@@ -1535,67 +1371,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-1.759705702369397</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>PC3</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>0.5907976080798988</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>PC3</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>0.6047210634087534</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>PC3</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>-1.542205563870714</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>PC3</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>-1.556677763635299</v>
+        <v>3.836272494677326</v>
       </c>
     </row>
   </sheetData>

--- a/MASTER/cluster_plots_loadings/agg/pca_results_agg.xlsx
+++ b/MASTER/cluster_plots_loadings/agg/pca_results_agg.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="agg_Loadings_Full" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="agg_Loadings_Top20" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="agg_Cluster_Means" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="agg_Cluster_StdDev" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="agg_Cluster_Counts" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="agg_Means_Long" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="agg_Loadings_Full" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="agg_Loadings_Top20" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="agg_Cluster_Means" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="agg_Cluster_StdDev" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="agg_Cluster_Counts" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="agg_Means_Long" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1157348996745892</v>
+        <v>0.1135707680189108</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1680546090256276</v>
+        <v>0.1743457149584376</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0009731086661451758</v>
+        <v>-0.0008595630820294929</v>
       </c>
       <c r="C3" t="n">
-        <v>0.06801481244504431</v>
+        <v>0.06723050390707008</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001116690510137621</v>
+        <v>0.001051728679301319</v>
       </c>
       <c r="C4" t="n">
-        <v>0.007838290360246204</v>
+        <v>0.007877734388425744</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01485059817299969</v>
+        <v>0.007881856112191828</v>
       </c>
       <c r="C5" t="n">
-        <v>0.46456309451552</v>
+        <v>0.4642250012442719</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.01491486038023693</v>
+        <v>-0.01658189283290849</v>
       </c>
       <c r="C6" t="n">
-        <v>0.04155987558594835</v>
+        <v>0.04048036993039653</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.06919850311731932</v>
+        <v>-0.08104756321874303</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6071411384687528</v>
+        <v>0.6023352625551539</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.08220537317096409</v>
+        <v>-0.08346545507025412</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4676192345389734</v>
+        <v>0.4635818182184262</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002662812684716794</v>
+        <v>0.001985357329268423</v>
       </c>
       <c r="C9" t="n">
-        <v>0.04644898335646994</v>
+        <v>0.04653574194719001</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.003550673906704603</v>
+        <v>-0.00384886924280596</v>
       </c>
       <c r="C10" t="n">
-        <v>0.01346980566927267</v>
+        <v>0.01329302213564386</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.004453983212853577</v>
+        <v>0.004398924674726379</v>
       </c>
       <c r="C11" t="n">
-        <v>0.01669204110145536</v>
+        <v>0.01698016659525952</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.01646364721566061</v>
+        <v>0.015640278992709</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.06789889884648816</v>
+        <v>-0.07078831792820577</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5397989313034232</v>
+        <v>0.5398846929473419</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2828436416323297</v>
+        <v>0.2977445703353754</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.002176486950230928</v>
+        <v>-0.002344831793756548</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.002585555619074323</v>
+        <v>-0.002773626894233348</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.01615010350602542</v>
+        <v>0.01566189479821756</v>
       </c>
       <c r="C15" t="n">
-        <v>0.06783823401477408</v>
+        <v>0.06867950143188849</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8258432170658452</v>
+        <v>0.8248606061118939</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.114273812707662</v>
+        <v>-0.1106956946134725</v>
       </c>
     </row>
     <row r="17">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.0005698876848640626</v>
+        <v>0.0005628429383246605</v>
       </c>
       <c r="C17" t="n">
-        <v>0.002135748655610592</v>
+        <v>0.002172614347008018</v>
       </c>
     </row>
     <row r="18">
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.02160004764652404</v>
+        <v>-0.02493594681390847</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1826484946121057</v>
+        <v>0.1815311275614516</v>
       </c>
     </row>
     <row r="19">
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.01244322254503104</v>
+        <v>-0.0139796413453283</v>
       </c>
       <c r="C19" t="n">
-        <v>0.03005764391480358</v>
+        <v>0.0292915210424969</v>
       </c>
     </row>
     <row r="20">
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.002244043359061231</v>
+        <v>0.002216303302366048</v>
       </c>
       <c r="C20" t="n">
-        <v>0.008409924822976518</v>
+        <v>0.008555090637495436</v>
       </c>
     </row>
     <row r="21">
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.003358172337800761</v>
+        <v>0.00104108581978435</v>
       </c>
       <c r="C21" t="n">
-        <v>0.151661465463071</v>
+        <v>0.1516615032275863</v>
       </c>
     </row>
   </sheetData>
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8258432170658452</v>
+        <v>0.8248606061118939</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.114273812707662</v>
+        <v>-0.1106956946134725</v>
       </c>
     </row>
     <row r="3">
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5397989313034232</v>
+        <v>0.5398846929473419</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2828436416323297</v>
+        <v>0.2977445703353754</v>
       </c>
     </row>
     <row r="4">
@@ -764,10 +764,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.06919850311731932</v>
+        <v>-0.08104756321874303</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6071411384687528</v>
+        <v>0.6023352625551539</v>
       </c>
     </row>
     <row r="5">
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.08220537317096409</v>
+        <v>-0.08346545507025412</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4676192345389734</v>
+        <v>0.4635818182184262</v>
       </c>
     </row>
     <row r="6">
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01485059817299969</v>
+        <v>0.007881856112191828</v>
       </c>
       <c r="C6" t="n">
-        <v>0.46456309451552</v>
+        <v>0.4642250012442719</v>
       </c>
     </row>
     <row r="7">
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1157348996745892</v>
+        <v>0.1135707680189108</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1680546090256276</v>
+        <v>0.1743457149584376</v>
       </c>
     </row>
     <row r="8">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.02160004764652404</v>
+        <v>-0.02493594681390847</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1826484946121057</v>
+        <v>0.1815311275614516</v>
       </c>
     </row>
     <row r="9">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.003358172337800761</v>
+        <v>0.00104108581978435</v>
       </c>
       <c r="C9" t="n">
-        <v>0.151661465463071</v>
+        <v>0.1516615032275863</v>
       </c>
     </row>
     <row r="10">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01646364721566061</v>
+        <v>0.015640278992709</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.06789889884648816</v>
+        <v>-0.07078831792820577</v>
       </c>
     </row>
     <row r="11">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.01615010350602542</v>
+        <v>0.01566189479821756</v>
       </c>
       <c r="C11" t="n">
-        <v>0.06783823401477408</v>
+        <v>0.06867950143188849</v>
       </c>
     </row>
     <row r="12">
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0009731086661451758</v>
+        <v>-0.0008595630820294929</v>
       </c>
       <c r="C12" t="n">
-        <v>0.06801481244504431</v>
+        <v>0.06723050390707008</v>
       </c>
     </row>
     <row r="13">
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.01491486038023693</v>
+        <v>-0.01658189283290849</v>
       </c>
       <c r="C13" t="n">
-        <v>0.04155987558594835</v>
+        <v>0.04048036993039653</v>
       </c>
     </row>
     <row r="14">
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.002662812684716794</v>
+        <v>0.001985357329268423</v>
       </c>
       <c r="C14" t="n">
-        <v>0.04644898335646994</v>
+        <v>0.04653574194719001</v>
       </c>
     </row>
     <row r="15">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.01244322254503104</v>
+        <v>-0.0139796413453283</v>
       </c>
       <c r="C15" t="n">
-        <v>0.03005764391480358</v>
+        <v>0.0292915210424969</v>
       </c>
     </row>
     <row r="16">
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.004453983212853577</v>
+        <v>0.004398924674726379</v>
       </c>
       <c r="C16" t="n">
-        <v>0.01669204110145536</v>
+        <v>0.01698016659525952</v>
       </c>
     </row>
     <row r="17">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.003550673906704603</v>
+        <v>-0.00384886924280596</v>
       </c>
       <c r="C17" t="n">
-        <v>0.01346980566927267</v>
+        <v>0.01329302213564386</v>
       </c>
     </row>
     <row r="18">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.002244043359061231</v>
+        <v>0.002216303302366048</v>
       </c>
       <c r="C18" t="n">
-        <v>0.008409924822976518</v>
+        <v>0.008555090637495436</v>
       </c>
     </row>
     <row r="19">
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.001116690510137621</v>
+        <v>0.001051728679301319</v>
       </c>
       <c r="C19" t="n">
-        <v>0.007838290360246204</v>
+        <v>0.007877734388425744</v>
       </c>
     </row>
     <row r="20">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.002176486950230928</v>
+        <v>-0.002344831793756548</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.002585555619074323</v>
+        <v>-0.002773626894233348</v>
       </c>
     </row>
     <row r="21">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.0005698876848640626</v>
+        <v>0.0005628429383246605</v>
       </c>
       <c r="C21" t="n">
-        <v>0.002135748655610592</v>
+        <v>0.002172614347008018</v>
       </c>
     </row>
   </sheetData>
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.225726585003693</v>
+        <v>4.74983281537278</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4201768051518999</v>
+        <v>1.090887736438717</v>
       </c>
     </row>
     <row r="3">
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-3.227562172924972</v>
+        <v>-3.323187591758096</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.9817659166880812</v>
+        <v>-1.057958692465069</v>
       </c>
     </row>
     <row r="4">
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.133144747243484</v>
+        <v>1.604871838675558</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.5647905338731611</v>
+        <v>-1.457208224569138</v>
       </c>
     </row>
     <row r="5">
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-2.736498202368519</v>
+        <v>-3.739555103476817</v>
       </c>
       <c r="C5" t="n">
-        <v>3.836272494677326</v>
+        <v>3.470858045496856</v>
       </c>
     </row>
   </sheetData>
@@ -1112,10 +1112,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.303952241171763</v>
+        <v>2.070071043800124</v>
       </c>
       <c r="C2" t="n">
-        <v>1.972977843009895</v>
+        <v>2.144158416364655</v>
       </c>
     </row>
     <row r="3">
@@ -1125,10 +1125,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5468954606992731</v>
+        <v>0.5670348141895911</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5695173293097336</v>
+        <v>0.5625801186415242</v>
       </c>
     </row>
     <row r="4">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.127807601783646</v>
+        <v>0.9193519913752781</v>
       </c>
       <c r="C4" t="n">
-        <v>1.857566990815179</v>
+        <v>1.235562139654611</v>
       </c>
     </row>
     <row r="5">
@@ -1151,10 +1151,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.310490597727751</v>
+        <v>0.8692227322787303</v>
       </c>
       <c r="C5" t="n">
-        <v>1.730648438290521</v>
+        <v>1.7047369014996</v>
       </c>
     </row>
   </sheetData>
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1266,7 +1266,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6.225726585003693</v>
+        <v>4.74983281537278</v>
       </c>
     </row>
     <row r="3">
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-3.227562172924972</v>
+        <v>-3.323187591758096</v>
       </c>
     </row>
     <row r="4">
@@ -1296,7 +1296,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2.133144747243484</v>
+        <v>1.604871838675558</v>
       </c>
     </row>
     <row r="5">
@@ -1311,7 +1311,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-2.736498202368519</v>
+        <v>-3.739555103476817</v>
       </c>
     </row>
     <row r="6">
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.4201768051518999</v>
+        <v>1.090887736438717</v>
       </c>
     </row>
     <row r="7">
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.9817659166880812</v>
+        <v>-1.057958692465069</v>
       </c>
     </row>
     <row r="8">
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.5647905338731611</v>
+        <v>-1.457208224569138</v>
       </c>
     </row>
     <row r="9">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3.836272494677326</v>
+        <v>3.470858045496856</v>
       </c>
     </row>
   </sheetData>

--- a/MASTER/cluster_plots_loadings/agg/pca_results_agg.xlsx
+++ b/MASTER/cluster_plots_loadings/agg/pca_results_agg.xlsx
@@ -1025,20 +1025,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>No oil, minerals</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.74983281537278</v>
+        <v>-3.739555103476817</v>
       </c>
       <c r="C2" t="n">
-        <v>1.090887736438717</v>
+        <v>3.470858045496856</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>No oil, no minerals</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1051,7 +1051,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Oil, no minerals</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1064,14 +1064,14 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Oil, some minerals</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-3.739555103476817</v>
+        <v>4.74983281537278</v>
       </c>
       <c r="C5" t="n">
-        <v>3.470858045496856</v>
+        <v>1.090887736438717</v>
       </c>
     </row>
   </sheetData>
@@ -1108,20 +1108,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>No oil, minerals</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.070071043800124</v>
+        <v>0.8692227322787303</v>
       </c>
       <c r="C2" t="n">
-        <v>2.144158416364655</v>
+        <v>1.7047369014996</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>No oil, no minerals</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1134,7 +1134,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Oil, no minerals</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1147,14 +1147,14 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Oil, some minerals</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8692227322787303</v>
+        <v>2.070071043800124</v>
       </c>
       <c r="C5" t="n">
-        <v>1.7047369014996</v>
+        <v>2.144158416364655</v>
       </c>
     </row>
   </sheetData>
@@ -1186,17 +1186,17 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>No oil, minerals</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>No oil, no minerals</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1206,7 +1206,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Oil, no minerals</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1216,11 +1216,11 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Oil, some minerals</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1257,7 +1257,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>No oil, minerals</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1266,13 +1266,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4.74983281537278</v>
+        <v>-3.739555103476817</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>No oil, no minerals</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1287,7 +1287,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Oil, no minerals</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1302,7 +1302,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Oil, some minerals</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-3.739555103476817</v>
+        <v>4.74983281537278</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>No oil, minerals</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1326,13 +1326,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.090887736438717</v>
+        <v>3.470858045496856</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>No oil, no minerals</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1347,7 +1347,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Oil, no minerals</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1362,7 +1362,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Oil, some minerals</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3.470858045496856</v>
+        <v>1.090887736438717</v>
       </c>
     </row>
   </sheetData>

--- a/MASTER/cluster_plots_loadings/agg/pca_results_agg.xlsx
+++ b/MASTER/cluster_plots_loadings/agg/pca_results_agg.xlsx
@@ -1025,20 +1025,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>No oil, minerals</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-3.739555103476817</v>
+        <v>4.74983281537278</v>
       </c>
       <c r="C2" t="n">
-        <v>3.470858045496856</v>
+        <v>1.090887736438717</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>No oil, no minerals</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1051,7 +1051,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Oil, no minerals</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1064,14 +1064,14 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Oil, some minerals</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.74983281537278</v>
+        <v>-3.739555103476817</v>
       </c>
       <c r="C5" t="n">
-        <v>1.090887736438717</v>
+        <v>3.470858045496856</v>
       </c>
     </row>
   </sheetData>
@@ -1108,20 +1108,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>No oil, minerals</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8692227322787303</v>
+        <v>2.070071043800124</v>
       </c>
       <c r="C2" t="n">
-        <v>1.7047369014996</v>
+        <v>2.144158416364655</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>No oil, no minerals</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1134,7 +1134,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Oil, no minerals</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1147,14 +1147,14 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Oil, some minerals</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.070071043800124</v>
+        <v>0.8692227322787303</v>
       </c>
       <c r="C5" t="n">
-        <v>2.144158416364655</v>
+        <v>1.7047369014996</v>
       </c>
     </row>
   </sheetData>
@@ -1186,17 +1186,17 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>No oil, minerals</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>No oil, no minerals</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1206,7 +1206,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Oil, no minerals</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1216,11 +1216,11 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Oil, some minerals</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1257,7 +1257,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>No oil, minerals</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1266,13 +1266,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-3.739555103476817</v>
+        <v>4.74983281537278</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>No oil, no minerals</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1287,7 +1287,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Oil, no minerals</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1302,7 +1302,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Oil, some minerals</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4.74983281537278</v>
+        <v>-3.739555103476817</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>No oil, minerals</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1326,13 +1326,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3.470858045496856</v>
+        <v>1.090887736438717</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>No oil, no minerals</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1347,7 +1347,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Oil, no minerals</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1362,7 +1362,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Oil, some minerals</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1.090887736438717</v>
+        <v>3.470858045496856</v>
       </c>
     </row>
   </sheetData>
